--- a/data/gold/results/01_eriksen_replication/table_1.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_1.xlsx
@@ -415,19 +415,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4864.111305166502</v>
+        <v>4608.260597065414</v>
       </c>
       <c r="C2">
-        <v>5595.226019299745</v>
+        <v>4261.281022540152</v>
       </c>
       <c r="D2">
-        <v>43.01963532551069</v>
+        <v>95.51845307556377</v>
       </c>
       <c r="E2">
-        <v>3833.21048095657</v>
+        <v>4855.583327817173</v>
       </c>
       <c r="F2">
-        <v>1479.458292819475</v>
+        <v>832.9090224620084</v>
       </c>
       <c r="G2">
         <v>40596.97766008925</v>
@@ -438,19 +438,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1972.465854892555</v>
+        <v>2427.290319893199</v>
       </c>
       <c r="C3">
-        <v>1861.983933522006</v>
+        <v>2274.251186755728</v>
       </c>
       <c r="D3">
-        <v>16.23503612216632</v>
+        <v>43.77887634536791</v>
       </c>
       <c r="E3">
-        <v>1653.666331477455</v>
+        <v>2991.265753386628</v>
       </c>
       <c r="F3">
-        <v>548.2617992242</v>
+        <v>491.2926439420454</v>
       </c>
       <c r="G3">
         <v>37552.28493467391</v>
@@ -461,19 +461,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1339.915588010944</v>
+        <v>1395.293259083857</v>
       </c>
       <c r="C4">
-        <v>2924.042064732495</v>
+        <v>1828.602963157943</v>
       </c>
       <c r="D4">
-        <v>20.05719459529767</v>
+        <v>49.50356888410434</v>
       </c>
       <c r="E4">
-        <v>1646.700904396185</v>
+        <v>1758.883308686225</v>
       </c>
       <c r="F4">
-        <v>700.9609017771467</v>
+        <v>304.651266670026</v>
       </c>
       <c r="G4">
         <v>1950.307677832142</v>
@@ -484,19 +484,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>921.1918622629997</v>
+        <v>155.1390180883685</v>
       </c>
       <c r="C5">
-        <v>781.6681210452316</v>
+        <v>130.8949726264793</v>
       </c>
       <c r="D5">
-        <v>6.536304608046691</v>
+        <v>2.044907846091662</v>
       </c>
       <c r="E5">
-        <v>531.0508450829358</v>
+        <v>103.6418657443282</v>
       </c>
       <c r="F5">
-        <v>230.2355918181278</v>
+        <v>36.96511184993731</v>
       </c>
       <c r="G5">
         <v>1094.385047583204</v>

--- a/data/gold/results/01_eriksen_replication/table_1.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_1.xlsx
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4608.260597065414</v>
+        <v>4629.139016586378</v>
       </c>
       <c r="C2">
         <v>4261.281022540152</v>
@@ -427,7 +427,7 @@
         <v>4855.583327817173</v>
       </c>
       <c r="F2">
-        <v>832.9090224620084</v>
+        <v>259.4180916719396</v>
       </c>
       <c r="G2">
         <v>40596.97766008925</v>
@@ -450,7 +450,7 @@
         <v>2991.265753386628</v>
       </c>
       <c r="F3">
-        <v>491.2926439420454</v>
+        <v>163.0339948110767</v>
       </c>
       <c r="G3">
         <v>37552.28493467391</v>
@@ -473,7 +473,7 @@
         <v>1758.883308686225</v>
       </c>
       <c r="F4">
-        <v>304.651266670026</v>
+        <v>90.18586013200851</v>
       </c>
       <c r="G4">
         <v>1950.307677832142</v>
@@ -496,7 +496,7 @@
         <v>103.6418657443282</v>
       </c>
       <c r="F5">
-        <v>36.96511184993731</v>
+        <v>6.198236728855719</v>
       </c>
       <c r="G5">
         <v>1094.385047583204</v>
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>12.7</v>
+        <v>12.5221119865</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>606.2380000000001</v>
+        <v>627.294307534464</v>
       </c>
       <c r="C8">
         <v>27.5319</v>

--- a/data/gold/results/01_eriksen_replication/table_1.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_1.xlsx
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4629.139016586378</v>
+        <v>4714.915864429138</v>
       </c>
       <c r="C2">
         <v>4261.281022540152</v>
@@ -438,7 +438,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>2427.290319893199</v>
+        <v>2464.343254364033</v>
       </c>
       <c r="C3">
         <v>2274.251186755728</v>
@@ -461,7 +461,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1395.293259083857</v>
+        <v>1441.976334595065</v>
       </c>
       <c r="C4">
         <v>1828.602963157943</v>
@@ -484,7 +484,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>155.1390180883685</v>
+        <v>157.1798559490685</v>
       </c>
       <c r="C5">
         <v>130.8949726264793</v>

--- a/data/gold/results/01_eriksen_replication/table_1.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_1.xlsx
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4714.915864429138</v>
+        <v>4713.367605953854</v>
       </c>
       <c r="C2">
         <v>4261.281022540152</v>
@@ -438,7 +438,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>2464.343254364033</v>
+        <v>2463.440015417837</v>
       </c>
       <c r="C3">
         <v>2274.251186755728</v>
@@ -461,7 +461,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1441.976334595065</v>
+        <v>1441.375185837561</v>
       </c>
       <c r="C4">
         <v>1828.602963157943</v>
@@ -484,7 +484,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>157.1798559490685</v>
+        <v>157.1359851774778</v>
       </c>
       <c r="C5">
         <v>130.8949726264793</v>

--- a/data/gold/results/01_eriksen_replication/table_1.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_1.xlsx
@@ -418,13 +418,13 @@
         <v>4713.367605953854</v>
       </c>
       <c r="C2">
-        <v>4261.281022540152</v>
+        <v>4259.384222540152</v>
       </c>
       <c r="D2">
-        <v>95.51845307556377</v>
+        <v>95.50495307556376</v>
       </c>
       <c r="E2">
-        <v>4855.583327817173</v>
+        <v>4855.460127817173</v>
       </c>
       <c r="F2">
         <v>259.4180916719396</v>
@@ -556,13 +556,13 @@
         <v>627.294307534464</v>
       </c>
       <c r="C8">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D8">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E8">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F8">
         <v>0</v>
